--- a/visa_appendices/DEQUAD_Financial_Model.xlsx
+++ b/visa_appendices/DEQUAD_Financial_Model.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -582,7 +582,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Starting cash: £3,000 (pooled founder capital)</t>
+          <t>Starting cash: £6,000 (£3,000 from each founder, pooled in the company bank)</t>
         </is>
       </c>
     </row>
@@ -596,196 +596,210 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Accelerator:   NatWest Accelerator (London) — office, legal and accountancy support</t>
+          <t>Accelerator:   NatWest Accelerator (London) — joined 16 March 2026.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">               provided in-kind for the first 12 months</t>
+          <t xml:space="preserve">               Office, legal and accountancy support provided in-kind for 12 months.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Currency:     GBP, net of VAT</t>
+          <t>Prior accel:   Santander Universities Pre-Incubator — completed 2025.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>Anchor pilot:  University of Bedfordshire (lead founder = former SU President 2021-2023).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Currency:     GBP, net of VAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Horizon:      3 years annual + Year-1 monthly cash flow</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>KEY MODEL ASSUMPTIONS (different from a typical seed-funded model)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Founders take NO salary in Q1-Q2 Y1 (living on personal savings)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Founders draw £1,500/month each from Q3 Y1 (once pre-seed lands)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Office, legal and accountancy carry a nominal £0 cash cost in Y1 because</t>
+          <t xml:space="preserve">  - Founders take NO salary in Q1-Q2 Y1 (living on personal savings)</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    those services are provided FREE by the NatWest Accelerator. £1,200 of</t>
+          <t xml:space="preserve">  - Founders draw £1,500/month each from Q3 Y1 (once pre-seed lands)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    out-of-programme Companies House / IP / overflow accountancy fees are budgeted.</t>
+          <t xml:space="preserve">  - Office, legal and accountancy carry a nominal £0 cash cost in Y1 because</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Marketing in Q1-Q2 Y1 is £0 cash — founder organic outreach only.</t>
+          <t xml:space="preserve">    those services are provided FREE by the NatWest Accelerator. £1,200 of</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">    out-of-programme Companies House / IP / overflow accountancy fees are budgeted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Marketing in Q1-Q2 Y1 is £0 cash — founder organic outreach only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  - Y1 starts with the existing MVP, so no upfront engineering capex.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>WORKBOOK STRUCTURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. P&amp;L 3yr            — Annual Profit &amp; Loss</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Cash Flow 3yr      — Annual cash flow forecast</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Cash Flow Y1 (mo)  — Monthly cash flow for Year 1</t>
+          <t xml:space="preserve">  1. P&amp;L 3yr            — Annual Profit &amp; Loss</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Balance Sheet 3yr  — Year-end balance sheets</t>
+          <t xml:space="preserve">  2. Cash Flow 3yr      — Annual cash flow forecast</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Revenue W1         — Revenue detail by service</t>
+          <t xml:space="preserve">  3. Cash Flow Y1 (mo)  — Monthly cash flow for Year 1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. Cost of Sales W2   — Direct cost detail</t>
+          <t xml:space="preserve">  4. Balance Sheet 3yr  — Year-end balance sheets</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7. Payroll W3         — Salaries, NI and pension</t>
+          <t xml:space="preserve">  5. Revenue W1         — Revenue detail by service</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8. Marketing W4       — Marketing spend by channel</t>
+          <t xml:space="preserve">  6. Cost of Sales W2   — Direct cost detail</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9. R&amp;D W5             — R&amp;D investment</t>
+          <t xml:space="preserve">  7. Payroll W3         — Salaries, NI and pension</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10. Fixed Assets       — CAPEX schedule</t>
+          <t xml:space="preserve">  8. Marketing W4       — Marketing spend by channel</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11. Accelerator Value  — Quantified in-kind value of NatWest support</t>
+          <t xml:space="preserve">  9. R&amp;D W5             — R&amp;D investment</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12. Startup Loan       — Empty (no debt taken)</t>
+          <t xml:space="preserve"> 10. Fixed Assets       — CAPEX schedule</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr"/>
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 11. Accelerator Value  — Quantified in-kind value of NatWest support</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"> 12. Startup Loan       — Empty (no debt taken)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
           <t>All assumptions map to /app/visa_appendices/DEQUAD_Envestors_Business_Plan.md.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>Yellow cells indicate user-editable inputs.</t>
         </is>
@@ -2149,10 +2163,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>134028</v>
+        <v>137028</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>824256</v>
+        <v>827256</v>
       </c>
     </row>
     <row r="7">
@@ -2172,7 +2186,7 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>0</v>
@@ -2252,7 +2266,7 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>164988</v>
+        <v>167988</v>
       </c>
       <c r="C13" s="12" t="n">
         <v>940308</v>
@@ -2438,7 +2452,7 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>134028</v>
+        <v>137028</v>
       </c>
       <c r="C27" s="12" t="n">
         <v>690228</v>
@@ -2454,13 +2468,13 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>134028</v>
+        <v>137028</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>824256</v>
+        <v>827256</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>890776</v>
+        <v>893776</v>
       </c>
     </row>
   </sheetData>
@@ -2599,40 +2613,40 @@
         <v>0</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>1540</v>
+        <v>4540</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>1210</v>
+        <v>4210</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>950</v>
+        <v>3950</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>670</v>
+        <v>3670</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>570</v>
+        <v>3570</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>550</v>
+        <v>3550</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>146680</v>
+        <v>149680</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>143350</v>
+        <v>146350</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>140310</v>
+        <v>143310</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>137590</v>
+        <v>140590</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>135300</v>
+        <v>138300</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>708720</v>
+        <v>741720</v>
       </c>
     </row>
     <row r="6">
@@ -2662,7 +2676,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>0</v>
@@ -2698,7 +2712,7 @@
         <v>0</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="8">
@@ -2800,7 +2814,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>0</v>
@@ -2836,7 +2850,7 @@
         <v>3188</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>164988</v>
+        <v>167988</v>
       </c>
     </row>
     <row r="11">
@@ -3372,43 +3386,43 @@
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>1540</v>
+        <v>4540</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>1210</v>
+        <v>4210</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>950</v>
+        <v>3950</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>670</v>
+        <v>3670</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>570</v>
+        <v>3570</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>550</v>
+        <v>3550</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>146680</v>
+        <v>149680</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>143350</v>
+        <v>146350</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>140310</v>
+        <v>143310</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>137590</v>
+        <v>140590</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>135300</v>
+        <v>138300</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>134028</v>
+        <v>137028</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>842748</v>
+        <v>878748</v>
       </c>
     </row>
     <row r="25">
@@ -3532,13 +3546,13 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>134028</v>
+        <v>137028</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>824256</v>
+        <v>827256</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>890776</v>
+        <v>893776</v>
       </c>
     </row>
     <row r="11">
@@ -3580,13 +3594,13 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>134828</v>
+        <v>137828</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>830456</v>
+        <v>833456</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>912776</v>
+        <v>915776</v>
       </c>
     </row>
     <row r="15">
@@ -3596,13 +3610,13 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>135428</v>
+        <v>138428</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>832556</v>
+        <v>835556</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>919376</v>
+        <v>922376</v>
       </c>
     </row>
     <row r="17">
@@ -3670,13 +3684,13 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>134028</v>
+        <v>137028</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>828356</v>
+        <v>831356</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>909576</v>
+        <v>912576</v>
       </c>
     </row>
     <row r="24">
@@ -3760,13 +3774,13 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>-600</v>
+        <v>2400</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>6500</v>
+        <v>9500</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>26200</v>
+        <v>29200</v>
       </c>
     </row>
   </sheetData>

--- a/visa_appendices/DEQUAD_Financial_Model.xlsx
+++ b/visa_appendices/DEQUAD_Financial_Model.xlsx
@@ -561,7 +561,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Prepared for: Envestors (endorsing body) — UK Innovator Founder Visa</t>
+          <t>Prepared for: UKES (endorsing body) — UK Innovator Founder Visa</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>All assumptions map to /app/visa_appendices/DEQUAD_Envestors_Business_Plan.md.</t>
+          <t>All assumptions map to /app/visa_appendices/DEQUAD_UKES_Business_Plan.md.</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>The NatWest Accelerator membership materially de-risks Year 1: £31k of services received in-kind against just £1.2k of cash cost. This is a strong validation signal for Envestors — DEQUAD has already passed NatWest's selection process and is being mentored by their startup network.</t>
+          <t>The NatWest Accelerator membership materially de-risks Year 1: £31k of services received in-kind against just £1.2k of cash cost. This is a strong validation signal for UKES — DEQUAD has already passed NatWest's selection process and is being mentored by their startup network.</t>
         </is>
       </c>
     </row>

--- a/visa_appendices/DEQUAD_Financial_Model.xlsx
+++ b/visa_appendices/DEQUAD_Financial_Model.xlsx
@@ -2528,73 +2528,73 @@
       <c r="B4" s="6" t="inlineStr">
         <is>
           <t>M1
+Jun</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>M2
+Jul</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>M3
+Aug</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>M4
+Sep</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>M5
+Oct</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>M6
+Nov</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>M7
+Dec</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>M8
+Jan</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>M9
+Feb</t>
+        </is>
+      </c>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>M10
 Mar</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>M2
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>M11
 Apr</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>M3
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>M12
 May</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>M4
-Jun</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>M5
-Jul</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>M6
-Aug</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>M7
-Sep</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>M8
-Oct</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>M9
-Nov</t>
-        </is>
-      </c>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>M10
-Dec</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>M11
-Jan</t>
-        </is>
-      </c>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>M12
-Feb</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">

--- a/visa_appendices/DEQUAD_Financial_Model.xlsx
+++ b/visa_appendices/DEQUAD_Financial_Model.xlsx
@@ -1525,16 +1525,16 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>90000</v>
+        <v>80000</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>320000</v>
+        <v>280000</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>416000</v>
+        <v>370000</v>
       </c>
     </row>
     <row r="7">
@@ -1582,16 +1582,16 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>11988</v>
+        <v>15988</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>185808</v>
+        <v>175808</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>699280</v>
+        <v>659280</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>897076</v>
+        <v>851076</v>
       </c>
     </row>
     <row r="11">
@@ -1726,16 +1726,16 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>10548</v>
+        <v>14548</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>170208</v>
+        <v>160208</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>645280</v>
+        <v>605280</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>826036</v>
+        <v>780036</v>
       </c>
     </row>
     <row r="20">
@@ -1746,17 +1746,17 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>91.6%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr"/>
@@ -1988,16 +1988,16 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>-18072</v>
+        <v>-14072</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>-61272</v>
+        <v>-71272</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>66020</v>
+        <v>26020</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>-13324</v>
+        <v>-59324</v>
       </c>
     </row>
     <row r="36">
@@ -2008,17 +2008,17 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>-150.8%</t>
+          <t>-88.0%</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>-33.0%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr"/>
@@ -2049,16 +2049,16 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>-18372</v>
+        <v>-14372</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>-62772</v>
+        <v>-72772</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>61520</v>
+        <v>21520</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>-19624</v>
+        <v>-65624</v>
       </c>
     </row>
     <row r="39">
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>-18372</v>
+        <v>-14372</v>
       </c>
       <c r="C40" s="12" t="n">
-        <v>-62772</v>
+        <v>-72772</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>61520</v>
+        <v>21520</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>-19624</v>
+        <v>-65624</v>
       </c>
     </row>
   </sheetData>
@@ -2163,10 +2163,10 @@
         <v>0</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>137028</v>
+        <v>141028</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>827256</v>
+        <v>821256</v>
       </c>
     </row>
     <row r="7">
@@ -2250,13 +2250,13 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>11988</v>
+        <v>15988</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>185808</v>
+        <v>175808</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>699280</v>
+        <v>659280</v>
       </c>
     </row>
     <row r="13">
@@ -2266,13 +2266,13 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>167988</v>
+        <v>171988</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>940308</v>
+        <v>930308</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>708780</v>
+        <v>668780</v>
       </c>
     </row>
     <row r="15">
@@ -2452,13 +2452,13 @@
         </is>
       </c>
       <c r="B27" s="12" t="n">
-        <v>137028</v>
+        <v>141028</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>690228</v>
+        <v>680228</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>66520</v>
+        <v>26520</v>
       </c>
     </row>
     <row r="28">
@@ -2468,13 +2468,13 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>137028</v>
+        <v>141028</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>827256</v>
+        <v>821256</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>893776</v>
+        <v>847776</v>
       </c>
     </row>
   </sheetData>
@@ -3428,7 +3428,7 @@
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>Cash is positive every month: the £3,000 founder equity covers operating costs until the pre-seed bridge lands in M7 (September). Q1 marketing spend is intentionally £0 — early traction is from founder-led university outreach and the existing beta cohort.</t>
+          <t>Cash is positive every month: the £3,000 founder equity covers operating costs until the pre-seed bridge lands in M7 (December). Q1 marketing spend is intentionally £0 — early traction is from founder-led university outreach and the existing beta cohort.</t>
         </is>
       </c>
     </row>
@@ -3546,13 +3546,13 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>137028</v>
+        <v>141028</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>827256</v>
+        <v>821256</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>893776</v>
+        <v>847776</v>
       </c>
     </row>
     <row r="11">
@@ -3594,13 +3594,13 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>137828</v>
+        <v>141828</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>833456</v>
+        <v>827456</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>915776</v>
+        <v>869776</v>
       </c>
     </row>
     <row r="15">
@@ -3610,13 +3610,13 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>138428</v>
+        <v>142428</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>835556</v>
+        <v>829556</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>922376</v>
+        <v>876376</v>
       </c>
     </row>
     <row r="17">
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>137028</v>
+        <v>141028</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>831356</v>
+        <v>825356</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>912576</v>
+        <v>866576</v>
       </c>
     </row>
     <row r="24">
@@ -3742,13 +3742,13 @@
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>-18372</v>
+        <v>-14372</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>-81144</v>
+        <v>-87144</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>-19624</v>
+        <v>-65624</v>
       </c>
     </row>
     <row r="28">
@@ -3758,13 +3758,13 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>134628</v>
+        <v>138628</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>821856</v>
+        <v>815856</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>883376</v>
+        <v>837376</v>
       </c>
     </row>
     <row r="30">
@@ -3797,7 +3797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -3850,16 +3850,16 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>11988</v>
+        <v>15988</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>185808</v>
+        <v>175808</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>699280</v>
+        <v>659280</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>897076</v>
+        <v>851076</v>
       </c>
     </row>
     <row r="7">
@@ -3914,174 +3914,212 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
+          <t>Price per enrolled student (£/yr)</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Average enrolled students per institution</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
           <t>Average contract value (£/yr)</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>14000</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>16000</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>42000</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="B12" s="10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>Subtotal revenue</t>
         </is>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B13" s="12" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>280000</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>Service 2 — DEQUAD Premium (B2C)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Paying student subs (avg, year)</t>
+        </is>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D16" s="10" t="n">
         <v>6000</v>
       </c>
-      <c r="C11" s="12" t="n">
-        <v>90000</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>320000</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>416000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>Service 2 — DEQUAD Premium (B2C)</t>
-        </is>
-      </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
-      <c r="E13" s="8" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Paying student subs (avg, year)</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n">
-        <v>100</v>
-      </c>
-      <c r="C14" s="10" t="n">
-        <v>1600</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E14" s="10" t="n">
+      <c r="E16" s="10" t="n">
         <v>7700</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Price per student (£/month)</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B17" s="10" t="n">
         <v>4.99</v>
       </c>
-      <c r="C15" s="10" t="n">
+      <c r="C17" s="10" t="n">
         <v>4.99</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D17" s="10" t="n">
         <v>4.99</v>
       </c>
-      <c r="E15" s="10" t="n">
+      <c r="E17" s="10" t="n">
         <v>14.97</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>Subtotal revenue</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
+      <c r="B18" s="12" t="n">
         <v>5988</v>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C18" s="12" t="n">
         <v>95808</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="D18" s="12" t="n">
         <v>359280</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>461076</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>Service 3 — NHS ICB pilot</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
-      <c r="E18" s="8" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="B20" s="8" t="n"/>
+      <c r="C20" s="8" t="n"/>
+      <c r="D20" s="8" t="n"/>
+      <c r="E20" s="8" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Number of contracts</t>
         </is>
       </c>
-      <c r="B19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="10" t="n">
+      <c r="B21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="10" t="n">
+      <c r="E21" s="10" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>Average contract value (£/yr)</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" s="10" t="n">
+      <c r="B22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="10" t="n">
         <v>20000</v>
       </c>
-      <c r="E20" s="10" t="n">
+      <c r="E22" s="10" t="n">
         <v>20000</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
         <is>
           <t>Subtotal revenue</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="12" t="n">
+      <c r="B23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>20000</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E23" s="12" t="n">
         <v>20000</v>
       </c>
     </row>

--- a/visa_appendices/DEQUAD_Financial_Model.xlsx
+++ b/visa_appendices/DEQUAD_Financial_Model.xlsx
@@ -125,7 +125,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -156,12 +156,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -542,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A39"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -551,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>DEQUAD — Financial Model (Bootstrap Edition)</t>
+          <t>DEQUAD — Financial Model (Self-Funded 3-Year Edition)</t>
         </is>
       </c>
     </row>
@@ -575,231 +569,294 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Founders:     Two co-founders — Founder A (Yusuf Quadri) and Founder B (TBC)</t>
+          <t>Founders:     Two co-founders — Yusuf Quadri (CEO) and Yusuff Adeagbo (CTO)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Starting cash: £6,000 (£3,000 from each founder, pooled in the company bank)</t>
+          <t>Starting cash: £6,000 (£3,000 from each founder, pooled in the company bank) —</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>MVP status:    Production-ready and deployed at https://dequad.co.uk</t>
+          <t xml:space="preserve">               the ONLY funding assumed anywhere in this model.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Accelerator:   NatWest Accelerator (London) — joined 16 March 2026.</t>
+          <t>MVP status:    Production-ready and deployed at https://dequad.co.uk</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">               Office, legal and accountancy support provided in-kind for 12 months.</t>
+          <t>Accelerator:   NatWest Accelerator (London) — joined 16 March 2026.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Prior accel:   Santander Universities Pre-Incubator — completed 2025.</t>
+          <t xml:space="preserve">               Office, legal and accountancy support provided in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Anchor pilot:  University of Bedfordshire (lead founder = former SU President 2021-2023).</t>
+          <t>Prior accel:   Santander Universities Pre-Incubator — completed 2025.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Currency:     GBP, net of VAT</t>
+          <t>Pilot status:  Early, informal conversation with University of Bedfordshire (lead</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Horizon:      3 years annual + Year-1 monthly cash flow</t>
+          <t xml:space="preserve">               founder = former SU President 2021-2023). NO agreement, LOI or date</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               is signed. Modelled as a Y2 upside only — never assumed in Y1.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>KEY MODEL ASSUMPTIONS (different from a typical seed-funded model)</t>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Currency:      GBP, net of VAT</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Founders take NO salary in Q1-Q2 Y1 (living on personal savings)</t>
+          <t>Horizon:       3 years annual + Year-1 monthly cash flow</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Founders draw £1,500/month each from Q3 Y1 (once pre-seed lands)</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Office, legal and accountancy carry a nominal £0 cash cost in Y1 because</t>
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>KEY MODEL ASSUMPTIONS (deliberately conservative and self-funded)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    those services are provided FREE by the NatWest Accelerator. £1,200 of</t>
+          <t xml:space="preserve">  - NO pre-seed, seed, Series A, grant or R&amp;D tax credit is assumed anywhere.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    out-of-programme Companies House / IP / overflow accountancy fees are budgeted.</t>
+          <t xml:space="preserve">  - Y1 institutional revenue is £0 — nothing is signed. Premium (B2C) revenue</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Marketing in Q1-Q2 Y1 is £0 cash — founder organic outreach only.</t>
+          <t xml:space="preserve">    is modelled independently of any pilot, from the existing 80-person</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Y1 starts with the existing MVP, so no upfront engineering capex.</t>
+          <t xml:space="preserve">    Bedfordshire beta cohort plus modest organic growth.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - Founders take NO salary in Y1 or Y2 (living on personal savings/freelance</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>WORKBOOK STRUCTURE</t>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    income). Modest £500/month each begins in Y3, funded entirely by revenue.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1. P&amp;L 3yr            — Annual Profit &amp; Loss</t>
+          <t xml:space="preserve">  - The plan's only funded hire (Safeguarding &amp; Trust Lead, part-time) starts</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  2. Cash Flow 3yr      — Annual cash flow forecast</t>
+          <t xml:space="preserve">    in Y3, contingent on 2+ paying universities, funded entirely by revenue.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Cash Flow Y1 (mo)  — Monthly cash flow for Year 1</t>
+          <t xml:space="preserve">  - Office, legal and accountancy carry a nominal £0 cash cost in Y1 because</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Balance Sheet 3yr  — Year-end balance sheets</t>
+          <t xml:space="preserve">    those services are provided FREE by the NatWest Accelerator (Y1 only).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Revenue W1         — Revenue detail by service</t>
+          <t xml:space="preserve">  - Marketing is founder-led and low-cost throughout — no paid-acquisition</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. Cost of Sales W2   — Direct cost detail</t>
+          <t xml:space="preserve">    budget in Y1; spend grows only in line with actual revenue in Y2-Y3.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7. Payroll W3         — Salaries, NI and pension</t>
+          <t xml:space="preserve">  - Y1 starts with the existing MVP, so no upfront engineering capex.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  8. Marketing W4       — Marketing spend by channel</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  9. R&amp;D W5             — R&amp;D investment</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>WORKBOOK STRUCTURE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10. Fixed Assets       — CAPEX schedule</t>
+          <t xml:space="preserve">  1. P&amp;L 3yr            — Annual Profit &amp; Loss</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11. Accelerator Value  — Quantified in-kind value of NatWest support</t>
+          <t xml:space="preserve">  2. Cash Flow 3yr      — Annual cash flow forecast</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12. Startup Loan       — Empty (no debt taken)</t>
+          <t xml:space="preserve">  3. Cash Flow Y1 (mo)  — Monthly cash flow for Year 1</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  4. Balance Sheet 3yr  — Year-end balance sheets</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>All assumptions map to /app/visa_appendices/DEQUAD_UKES_Business_Plan.md.</t>
+          <t xml:space="preserve">  5. Revenue W1         — Revenue detail by service</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  6. Cost of Sales W2   — Direct cost detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  7. Payroll W3         — Salaries, NI and pension</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  8. Marketing W4       — Marketing spend by channel</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  9. R&amp;D W5             — R&amp;D activity (unpaid founder time; no tax credit assumed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 10. Fixed Assets       — CAPEX schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 11. Accelerator Value  — Quantified in-kind value of NatWest support (Y1 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 12. Startup Loan       — Empty (no debt taken; no external funding assumed at all)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>All assumptions map to DEQUAD_UKES_Business_Plan.md (v5.0, self-funded revision).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>Yellow cells indicate user-editable inputs.</t>
         </is>
@@ -816,14 +873,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -836,7 +892,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -856,178 +912,92 @@
           <t>Year 3</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Total R&amp;D Cost (P&amp;L view)</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="n">
-        <v>22500</v>
-      </c>
-      <c r="C5" s="12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>110000</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>192500</v>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>R&amp;D delivery model</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="n"/>
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Founder time (unpaid, no cash cost)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Y1-Y2: 100%</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>Y1-Y2: 100%</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Some paid capacity from Y3</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Founder R&amp;D time (60% allocation Y1)</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="n">
-        <v>10800</v>
-      </c>
-      <c r="C7" s="10" t="n">
-        <v>28800</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <v>43200</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>82800</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>ML / NLP engineer time (allocated)</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>19200</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>64200</v>
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>Cash R&amp;D spend (already included in COGS/OPEX above)</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="n">
+        <v>400</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>900</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>1800</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>R&amp;D tooling &amp; datasets (HuggingFace, Modal)</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>19200</v>
-      </c>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>SME R&amp;D Tax Credit</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>3rd-party model evaluation &amp; safety testing</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>600</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>8600</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Hosting allocated to experiments</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>180</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>1400</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>3800</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>5380</v>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Assumed as a cash inflow in this model</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Compliance / DPIA work attributable to R&amp;D</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>720</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>2600</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>3320</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Estimated SME R&amp;D tax credit (16%)</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Receivable in following accounting period</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>9600</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>17600</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>30800</v>
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>R&amp;D is delivered as unpaid founder time throughout Y1-Y2, plus modest paid capacity from Y3 once revenue supports it. No SME R&amp;D Tax Credit inflow is assumed anywhere in this model — qualifying PAYE spend is minimal while founders are unpaid. The founders will explore claiming R&amp;D tax relief with NatWest's in-kind accountancy support once qualifying costs exist from Y3, as a possible upside not relied upon here.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:E2"/>
+  <mergeCells count="2">
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1063,7 +1033,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -1115,31 +1085,31 @@
           <t>Tangible — Laptops &amp; equipment</t>
         </is>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>33%</t>
         </is>
       </c>
-      <c r="C5" s="17" t="n">
-        <v>600</v>
-      </c>
-      <c r="D5" s="17" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F5" s="17" t="n">
-        <v>-200</v>
-      </c>
-      <c r="G5" s="17" t="n">
-        <v>-800</v>
-      </c>
-      <c r="H5" s="17" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="I5" s="17" t="n">
-        <v>4000</v>
+      <c r="C5" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="D5" s="15" t="n">
+        <v>500</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>900</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>-130</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>-340</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>-580</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>850</v>
       </c>
     </row>
     <row r="6">
@@ -1148,66 +1118,66 @@
           <t>Intangible — Capitalised R&amp;D (W5)</t>
         </is>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
         <is>
           <t>20%</t>
         </is>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="E6" s="15" t="n">
         <v>300</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="F6" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>-60</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-120</v>
+      </c>
+      <c r="I6" s="15" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Total CAPEX</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr"/>
+      <c r="C7" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="E7" s="12" t="n">
         <v>1200</v>
       </c>
-      <c r="E6" s="17" t="n">
-        <v>4000</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G6" s="17" t="n">
+      <c r="F7" s="12" t="n">
+        <v>-150</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>-400</v>
+      </c>
+      <c r="H7" s="12" t="n">
         <v>-700</v>
       </c>
-      <c r="H6" s="17" t="n">
-        <v>-2100</v>
-      </c>
-      <c r="I6" s="17" t="n">
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="18" t="inlineStr">
-        <is>
-          <t>Total CAPEX</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr"/>
-      <c r="C7" s="12" t="n">
-        <v>900</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>9000</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>-300</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>-1500</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>-4500</v>
-      </c>
       <c r="I7" s="12" t="n">
-        <v>6900</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>MVP is already built so the upfront capex is minimal. Y1 hardware = 2 laptops + 1 spare; Intangible adds are the cost of capitalised R&amp;D meeting IAS 38 criteria.</t>
+          <t>MVP is already built so upfront capex is minimal. Y1 hardware = 2 founder laptops; Y3 adds a laptop for the first part-time hire. Intangible adds are the cost of capitalised R&amp;D meeting IAS 38 criteria.</t>
         </is>
       </c>
     </row>
@@ -1237,14 +1207,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>NatWest Accelerator — Quantified In-Kind Value</t>
+          <t>NatWest Accelerator — Quantified In-Kind Value (Year 1 Only)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -1266,10 +1236,10 @@
           <t>Office co-working space (3 desks, central London)</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n">
+      <c r="B5" s="15" t="n">
         <v>12000</v>
       </c>
-      <c r="C5" s="17" t="n">
+      <c r="C5" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1279,10 +1249,10 @@
           <t>Legal advice (Mishcon de Reya, DLA Piper panels)</t>
         </is>
       </c>
-      <c r="B6" s="17" t="n">
+      <c r="B6" s="15" t="n">
         <v>4500</v>
       </c>
-      <c r="C6" s="17" t="n">
+      <c r="C6" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1292,10 +1262,10 @@
           <t>Accountancy support (PwC alumni network)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B7" s="15" t="n">
         <v>3600</v>
       </c>
-      <c r="C7" s="17" t="n">
+      <c r="C7" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1305,10 +1275,10 @@
           <t>Banking &amp; business introductions</t>
         </is>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B8" s="15" t="n">
         <v>2000</v>
       </c>
-      <c r="C8" s="17" t="n">
+      <c r="C8" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1318,10 +1288,10 @@
           <t>Investor pitch coaching &amp; mentoring</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B9" s="15" t="n">
         <v>5000</v>
       </c>
-      <c r="C9" s="17" t="n">
+      <c r="C9" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1331,10 +1301,10 @@
           <t>Programme demo day &amp; PR placement</t>
         </is>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B10" s="15" t="n">
         <v>4000</v>
       </c>
-      <c r="C10" s="17" t="n">
+      <c r="C10" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1344,11 +1314,11 @@
           <t>Out-of-programme costs (Companies House, IP filings)</t>
         </is>
       </c>
-      <c r="B11" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="17" t="n">
-        <v>1200</v>
+      <c r="B11" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="15" t="n">
+        <v>300</v>
       </c>
     </row>
     <row r="13">
@@ -1361,13 +1331,13 @@
         <v>31100</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>The NatWest Accelerator membership materially de-risks Year 1: £31k of services received in-kind against just £1.2k of cash cost. This is a strong validation signal for UKES — DEQUAD has already passed NatWest's selection process and is being mentored by their startup network.</t>
+          <t>The NatWest Accelerator membership materially de-risks Year 1: £31k of services received in-kind against a few hundred pounds of cash cost, covered within the £6,000 founder capital. This support runs for Year 1 only — from Year 2 the plan budgets modest real cash costs for office, legal and accountancy (see Cash Flow 3yr).</t>
         </is>
       </c>
     </row>
@@ -1389,7 +1359,7 @@
   <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -1406,7 +1376,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -1433,16 +1403,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
-        <is>
-          <t>No external debt taken at incorporation.</t>
+      <c r="A5" s="17" t="inlineStr">
+        <is>
+          <t>No external debt or equity taken at any point in this 3-year plan.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>The founders are bootstrapping with £3,000 of equity and the in-kind NatWest Accelerator support. The first cash injection is the £150,000 pre-seed bridge (equity, not debt) targeted for September Year 1 once the first paying university pilot has converted.</t>
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>The founders are self-funding the entire 3-year plan with £6,000 of equity plus revenue, and the in-kind NatWest Accelerator support in Year 1. No pre-seed, seed or other external investment is assumed, committed, or required for this plan to succeed. If institutional traction significantly exceeds this conservative forecast, the founders may explore external investment beyond Year 3 — that scenario is outside the scope of this model.</t>
         </is>
       </c>
     </row>
@@ -1481,7 +1451,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -1521,20 +1491,20 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Service 1 — University SaaS subscription</t>
+          <t>Service 1 — University SaaS subscription (contingent, not signed)</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="C6" s="10" t="n">
-        <v>80000</v>
-      </c>
       <c r="D6" s="10" t="n">
-        <v>280000</v>
+        <v>30000</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>370000</v>
+        <v>40000</v>
       </c>
     </row>
     <row r="7">
@@ -1544,22 +1514,22 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>5988</v>
+        <v>600</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>95808</v>
+        <v>6000</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>359280</v>
+        <v>18000</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>461076</v>
+        <v>24600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Service 3 — NHS ICB pilot</t>
+          <t>Service 3 — NHS ICB (not assumed in this 3-year plan)</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
@@ -1569,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>20000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1582,16 +1552,16 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>15988</v>
+        <v>600</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>175808</v>
+        <v>16000</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>659280</v>
+        <v>48000</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>851076</v>
+        <v>64600</v>
       </c>
     </row>
     <row r="11">
@@ -1612,16 +1582,16 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>5400</v>
+        <v>1200</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>18000</v>
+        <v>2400</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>23880</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="13">
@@ -1631,35 +1601,35 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>4200</v>
+        <v>900</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>14400</v>
+        <v>1800</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>18960</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Stripe processing (~2.9% + 30p)</t>
+          <t>Stripe processing</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D14" s="10" t="n">
         <v>180</v>
       </c>
-      <c r="C14" s="10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>12000</v>
-      </c>
       <c r="E14" s="10" t="n">
-        <v>15180</v>
+        <v>320</v>
       </c>
     </row>
     <row r="15">
@@ -1669,16 +1639,16 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1800</v>
+        <v>410</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>6000</v>
+        <v>800</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>7980</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="16">
@@ -1688,16 +1658,16 @@
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>3600</v>
+        <v>920</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>5040</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="17">
@@ -1707,35 +1677,35 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>1440</v>
+        <v>1400</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>15600</v>
+        <v>3100</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>54000</v>
+        <v>6100</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>71040</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Gross Profit</t>
+          <t>Gross Profit / (Loss)</t>
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>14548</v>
+        <v>-800</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>160208</v>
+        <v>12900</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>605280</v>
+        <v>41900</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>780036</v>
+        <v>54000</v>
       </c>
     </row>
     <row r="20">
@@ -1746,17 +1716,17 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>-133.3%</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>80.6%</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr"/>
@@ -1775,20 +1745,20 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Salaries (W3)</t>
+          <t>Salaries (W3) — £0 until Y3</t>
         </is>
       </c>
       <c r="B23" s="10" t="n">
-        <v>18000</v>
+        <v>0</v>
       </c>
       <c r="C23" s="10" t="n">
-        <v>156000</v>
+        <v>0</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>372000</v>
+        <v>20000</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>546000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="24">
@@ -1798,16 +1768,16 @@
         </is>
       </c>
       <c r="B24" s="10" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="C24" s="10" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="D24" s="10" t="n">
-        <v>38500</v>
+        <v>900</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>53700</v>
+        <v>900</v>
       </c>
     </row>
     <row r="25">
@@ -1817,16 +1787,16 @@
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>4680</v>
+        <v>0</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>11160</v>
+        <v>350</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>16380</v>
+        <v>350</v>
       </c>
     </row>
     <row r="26">
@@ -1836,16 +1806,16 @@
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>16000</v>
+        <v>250</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>22600</v>
+        <v>250</v>
       </c>
     </row>
     <row r="27">
@@ -1855,16 +1825,16 @@
         </is>
       </c>
       <c r="B27" s="10" t="n">
+        <v>600</v>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="D27" s="10" t="n">
         <v>1800</v>
       </c>
-      <c r="C27" s="10" t="n">
-        <v>6000</v>
-      </c>
-      <c r="D27" s="10" t="n">
-        <v>14400</v>
-      </c>
       <c r="E27" s="10" t="n">
-        <v>22200</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="28">
@@ -1877,13 +1847,13 @@
         <v>0</v>
       </c>
       <c r="C28" s="10" t="n">
-        <v>6000</v>
+        <v>300</v>
       </c>
       <c r="D28" s="10" t="n">
-        <v>12000</v>
+        <v>600</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>18000</v>
+        <v>900</v>
       </c>
     </row>
     <row r="29">
@@ -1893,16 +1863,16 @@
         </is>
       </c>
       <c r="B29" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <v>600</v>
+      </c>
+      <c r="D29" s="10" t="n">
         <v>1200</v>
       </c>
-      <c r="C29" s="10" t="n">
-        <v>5400</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <v>11000</v>
-      </c>
       <c r="E29" s="10" t="n">
-        <v>17600</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="30">
@@ -1912,16 +1882,16 @@
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>28000</v>
+        <v>2500</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>92000</v>
+        <v>5000</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>123600</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="31">
@@ -1934,13 +1904,13 @@
         <v>480</v>
       </c>
       <c r="C31" s="10" t="n">
-        <v>1800</v>
+        <v>700</v>
       </c>
       <c r="D31" s="10" t="n">
-        <v>3200</v>
+        <v>900</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>5480</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="32">
@@ -1950,16 +1920,16 @@
         </is>
       </c>
       <c r="B32" s="10" t="n">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="C32" s="10" t="n">
-        <v>3600</v>
+        <v>700</v>
       </c>
       <c r="D32" s="10" t="n">
-        <v>9000</v>
+        <v>1000</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>13800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="33">
@@ -1969,16 +1939,16 @@
         </is>
       </c>
       <c r="B33" s="12" t="n">
-        <v>28620</v>
+        <v>2680</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>231480</v>
+        <v>6000</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>579260</v>
+        <v>32000</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>839360</v>
+        <v>40680</v>
       </c>
     </row>
     <row r="35">
@@ -1988,16 +1958,16 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>-14072</v>
+        <v>-3480</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>-71272</v>
+        <v>6900</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>26020</v>
+        <v>9900</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>-59324</v>
+        <v>13320</v>
       </c>
     </row>
     <row r="36">
@@ -2008,17 +1978,17 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>-88.0%</t>
+          <t>-580.0%</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr"/>
@@ -2030,16 +2000,16 @@
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>-300</v>
+        <v>-150</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>-1500</v>
+        <v>-400</v>
       </c>
       <c r="D37" s="10" t="n">
-        <v>-4500</v>
+        <v>-700</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>-6300</v>
+        <v>-1250</v>
       </c>
     </row>
     <row r="38">
@@ -2049,35 +2019,35 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>-14372</v>
+        <v>-3630</v>
       </c>
       <c r="C38" s="12" t="n">
-        <v>-72772</v>
+        <v>6500</v>
       </c>
       <c r="D38" s="12" t="n">
-        <v>21520</v>
+        <v>9200</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>-65624</v>
+        <v>12070</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Corporation Tax</t>
+          <t>Corporation Tax (paid in arrears — see Cash Flow)</t>
         </is>
       </c>
       <c r="B39" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C39" s="10" t="n">
-        <v>0</v>
+        <v>-500</v>
       </c>
       <c r="D39" s="10" t="n">
-        <v>0</v>
+        <v>-1200</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>-1700</v>
       </c>
     </row>
     <row r="40">
@@ -2087,16 +2057,16 @@
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>-14372</v>
+        <v>-3630</v>
       </c>
       <c r="C40" s="12" t="n">
-        <v>-72772</v>
+        <v>6000</v>
       </c>
       <c r="D40" s="12" t="n">
-        <v>21520</v>
+        <v>8000</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>-65624</v>
+        <v>10370</v>
       </c>
     </row>
   </sheetData>
@@ -2125,14 +2095,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Annual Cash Flow Forecast</t>
+          <t>Annual Cash Flow Forecast (Self-Funded)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -2160,325 +2130,295 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>141028</v>
+        <v>1920</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>821256</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
+        <v>8220</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (Year 1 opening = £6,000 founder equity, already invested Day 1)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr"/>
+      <c r="D6" s="13" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>RECEIPTS</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Founder equity injection (Day 1)</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0</v>
-      </c>
+      <c r="B8" s="8" t="n"/>
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Pre-seed equity (Q3 Y1 — £150k @ £1.2m cap)</t>
+          <t>Cash from sales (collected)</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>150000</v>
+        <v>600</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Seed equity (Y2 — £750k @ £6m post)</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>750000</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>R&amp;D tax credit received</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>4500</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>9500</v>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Total Receipts</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>48000</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Cash from sales (collected)</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>15988</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>175808</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>659280</v>
-      </c>
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>EXPENDITURE</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n"/>
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="8" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Total Receipts</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>171988</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>930308</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>668780</v>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>Cost of sales</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
+        <v>-1400</v>
+      </c>
+      <c r="C13" s="10" t="n">
+        <v>-3100</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <v>-6100</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Payroll (gross + NI + pension + benefits)</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="10" t="n">
+        <v>-21500</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>EXPENDITURE</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>-900</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>-2500</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>-5000</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Cost of sales</t>
+          <t>Software subscriptions</t>
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>-1440</v>
+        <v>-600</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>-15600</v>
+        <v>-1200</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>-54000</v>
+        <v>-1800</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Payroll (gross + NI + pension + benefits)</t>
+          <t>Office (£0 Y1 — NatWest Accelerator)</t>
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>-20340</v>
+        <v>0</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>-180680</v>
+        <v>-300</v>
       </c>
       <c r="D17" s="10" t="n">
-        <v>-437660</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Legal &amp; accountancy (out-of-programme)</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>-3600</v>
+        <v>-300</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>-28000</v>
+        <v>-600</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>-92000</v>
+        <v>-1200</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Software subscriptions</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>-1800</v>
+        <v>-480</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>-6000</v>
+        <v>-700</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>-14400</v>
+        <v>-900</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Office (£0 Y1 — NatWest Accelerator)</t>
+          <t>Business support / misc</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="C20" s="10" t="n">
-        <v>-6000</v>
+        <v>-700</v>
       </c>
       <c r="D20" s="10" t="n">
-        <v>-12000</v>
+        <v>-1000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Legal &amp; accountancy (out-of-programme)</t>
+          <t>Fixed assets capex</t>
         </is>
       </c>
       <c r="B21" s="10" t="n">
+        <v>-600</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>-600</v>
+      </c>
+      <c r="D21" s="10" t="n">
         <v>-1200</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>-5400</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>-11000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Corporation tax (prior-year liability, paid in arrears)</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>-480</v>
+        <v>0</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>-1800</v>
+        <v>0</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>-3200</v>
+        <v>-500</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Business support / misc</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="n">
-        <v>-1200</v>
-      </c>
-      <c r="C23" s="10" t="n">
-        <v>-3600</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>-9000</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Fixed assets &amp; R&amp;D capex</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="n">
-        <v>-900</v>
-      </c>
-      <c r="C24" s="10" t="n">
-        <v>-3000</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>-9000</v>
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>Total Expenditure</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n">
+        <v>-4680</v>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>-9700</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>-39800</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Total Expenditure</t>
+          <t>Cash surplus / (deficit)</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>-30960</v>
+        <v>-4080</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>-250080</v>
+        <v>6300</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>-642260</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>Cash surplus / (deficit)</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n">
-        <v>141028</v>
-      </c>
-      <c r="C27" s="12" t="n">
-        <v>680228</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>26520</v>
+        <v>8200</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>Closing cash balance</t>
+        </is>
+      </c>
+      <c r="B26" s="12" t="n">
+        <v>1920</v>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>8220</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>16420</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Closing cash balance</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n">
-        <v>141028</v>
-      </c>
-      <c r="C28" s="12" t="n">
-        <v>821256</v>
-      </c>
-      <c r="D28" s="12" t="n">
-        <v>847776</v>
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>No pre-seed, seed, Series A, grant or R&amp;D tax credit is assumed anywhere in this table. Closing cash stays positive every year, funded entirely by the £6,000 founder capital plus revenue — the plan does not depend on any pilot converting or any investor closing.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A28:D28"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2491,7 +2431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2513,14 +2453,14 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Year 1 Monthly Cash Flow Forecast (Bootstrap)</t>
+          <t>Year 1 Monthly Cash Flow Forecast (Self-Funded)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -2610,43 +2550,43 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>4540</v>
+        <v>4965</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>4210</v>
+        <v>4830</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>3950</v>
+        <v>4587</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>3670</v>
+        <v>4304</v>
       </c>
       <c r="G5" s="10" t="n">
-        <v>3570</v>
+        <v>4011</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>3550</v>
+        <v>3708</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>149680</v>
+        <v>3435</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>146350</v>
+        <v>3172</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>143310</v>
+        <v>2919</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>140590</v>
+        <v>2676</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>138300</v>
+        <v>2443</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>741720</v>
+        <v>47050</v>
       </c>
     </row>
     <row r="6">
@@ -2672,11 +2612,11 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Founder equity</t>
+          <t xml:space="preserve">  Cash from premium (B2C) sales — Stripe live from M7</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>0</v>
@@ -2694,235 +2634,235 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="M7" s="10" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="N7" s="10" t="n">
-        <v>6000</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Pre-seed equity (Q3)</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <v>150000</v>
-      </c>
-      <c r="I8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="10" t="n">
-        <v>150000</v>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Total Receipts</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="I8" s="12" t="n">
+        <v>70</v>
+      </c>
+      <c r="J8" s="12" t="n">
+        <v>90</v>
+      </c>
+      <c r="K8" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="L8" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="M8" s="12" t="n">
+        <v>150</v>
+      </c>
+      <c r="N8" s="12" t="n">
+        <v>600</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cash from sales</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>200</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>350</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>500</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>700</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>800</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>1100</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>1350</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>1700</v>
-      </c>
-      <c r="L9" s="10" t="n">
-        <v>2100</v>
-      </c>
-      <c r="M9" s="10" t="n">
-        <v>3188</v>
-      </c>
-      <c r="N9" s="10" t="n">
-        <v>11988</v>
-      </c>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>EXPENDITURE</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="n"/>
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="8" t="n"/>
+      <c r="E9" s="8" t="n"/>
+      <c r="F9" s="8" t="n"/>
+      <c r="G9" s="8" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
+      <c r="J9" s="8" t="n"/>
+      <c r="K9" s="8" t="n"/>
+      <c r="L9" s="8" t="n"/>
+      <c r="M9" s="8" t="n"/>
+      <c r="N9" s="8" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
-        <is>
-          <t>Total Receipts</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>200</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>350</v>
-      </c>
-      <c r="F10" s="12" t="n">
-        <v>500</v>
-      </c>
-      <c r="G10" s="12" t="n">
-        <v>700</v>
-      </c>
-      <c r="H10" s="12" t="n">
-        <v>150800</v>
-      </c>
-      <c r="I10" s="12" t="n">
-        <v>1100</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>1350</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>1700</v>
-      </c>
-      <c r="L10" s="12" t="n">
-        <v>2100</v>
-      </c>
-      <c r="M10" s="12" t="n">
-        <v>3188</v>
-      </c>
-      <c r="N10" s="12" t="n">
-        <v>167988</v>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cost of sales</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>-60</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>-60</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>-70</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>-80</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>-90</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>-100</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>-110</v>
+      </c>
+      <c r="I10" s="10" t="n">
+        <v>-120</v>
+      </c>
+      <c r="J10" s="10" t="n">
+        <v>-130</v>
+      </c>
+      <c r="K10" s="10" t="n">
+        <v>-140</v>
+      </c>
+      <c r="L10" s="10" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>-290</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>-1400</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>EXPENDITURE</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="8" t="n"/>
-      <c r="M11" s="8" t="n"/>
-      <c r="N11" s="8" t="n"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Software subscriptions</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="H11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="M11" s="10" t="n">
+        <v>-50</v>
+      </c>
+      <c r="N11" s="10" t="n">
+        <v>-600</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Cost of sales</t>
+          <t xml:space="preserve">  Legal &amp; accountancy (incorporation, IP filings)</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>-30</v>
+        <v>-300</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>-70</v>
+        <v>0</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>-110</v>
+        <v>0</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>-130</v>
+        <v>0</v>
       </c>
       <c r="H12" s="10" t="n">
-        <v>-140</v>
+        <v>0</v>
       </c>
       <c r="I12" s="10" t="n">
-        <v>-150</v>
+        <v>0</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>-160</v>
+        <v>0</v>
       </c>
       <c r="K12" s="10" t="n">
-        <v>-180</v>
+        <v>0</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="M12" s="10" t="n">
-        <v>-130</v>
+        <v>0</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>-1440</v>
+        <v>-300</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Founder salaries (from M7 only)</t>
+          <t xml:space="preserve">  Insurance</t>
         </is>
       </c>
       <c r="B13" s="10" t="n">
@@ -2932,43 +2872,43 @@
         <v>0</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="F13" s="10" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="H13" s="10" t="n">
-        <v>-3000</v>
+        <v>-48</v>
       </c>
       <c r="I13" s="10" t="n">
-        <v>-3000</v>
+        <v>-48</v>
       </c>
       <c r="J13" s="10" t="n">
-        <v>-3000</v>
+        <v>-48</v>
       </c>
       <c r="K13" s="10" t="n">
-        <v>-3000</v>
+        <v>-48</v>
       </c>
       <c r="L13" s="10" t="n">
-        <v>-3000</v>
+        <v>-48</v>
       </c>
       <c r="M13" s="10" t="n">
-        <v>-3000</v>
+        <v>-48</v>
       </c>
       <c r="N13" s="10" t="n">
-        <v>-18000</v>
+        <v>-480</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Employer NI + pension + benefits</t>
+          <t xml:space="preserve">  Marketing (founder-led, low-cost)</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
@@ -2978,463 +2918,233 @@
         <v>0</v>
       </c>
       <c r="D14" s="10" t="n">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="F14" s="10" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="H14" s="10" t="n">
-        <v>-390</v>
+        <v>-90</v>
       </c>
       <c r="I14" s="10" t="n">
-        <v>-390</v>
+        <v>-90</v>
       </c>
       <c r="J14" s="10" t="n">
-        <v>-390</v>
+        <v>-90</v>
       </c>
       <c r="K14" s="10" t="n">
-        <v>-390</v>
+        <v>-90</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>-390</v>
+        <v>-90</v>
       </c>
       <c r="M14" s="10" t="n">
-        <v>-390</v>
+        <v>-160</v>
       </c>
       <c r="N14" s="10" t="n">
-        <v>-2340</v>
+        <v>-900</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Marketing</t>
+          <t xml:space="preserve">  Business support / misc</t>
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>0</v>
+        <v>-125</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="D15" s="10" t="n">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>-150</v>
+        <v>-25</v>
       </c>
       <c r="F15" s="10" t="n">
-        <v>-200</v>
+        <v>-25</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>-300</v>
+        <v>-25</v>
       </c>
       <c r="H15" s="10" t="n">
-        <v>-500</v>
+        <v>-25</v>
       </c>
       <c r="I15" s="10" t="n">
-        <v>-550</v>
+        <v>-25</v>
       </c>
       <c r="J15" s="10" t="n">
-        <v>-550</v>
+        <v>-25</v>
       </c>
       <c r="K15" s="10" t="n">
-        <v>-450</v>
+        <v>-25</v>
       </c>
       <c r="L15" s="10" t="n">
+        <v>-25</v>
+      </c>
+      <c r="M15" s="10" t="n">
+        <v>-25</v>
+      </c>
+      <c r="N15" s="10" t="n">
         <v>-400</v>
-      </c>
-      <c r="M15" s="10" t="n">
-        <v>-400</v>
-      </c>
-      <c r="N15" s="10" t="n">
-        <v>-3600</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Software subscriptions</t>
+          <t xml:space="preserve">  Fixed assets capex</t>
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>-700</v>
+        <v>-500</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="D16" s="10" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="10" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="H16" s="10" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I16" s="10" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="J16" s="10" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K16" s="10" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M16" s="10" t="n">
         <v>-100</v>
       </c>
       <c r="N16" s="10" t="n">
-        <v>-1800</v>
+        <v>-600</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Office (NatWest Accelerator — £0)</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="10" t="n">
-        <v>0</v>
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Total Expenditure</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>-1035</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>-135</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>-243</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>-283</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>-293</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>-303</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>-323</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>-333</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>-343</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>-353</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>-363</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>-673</v>
+      </c>
+      <c r="N17" s="12" t="n">
+        <v>-4680</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Legal &amp; accountancy (out-of-programme)</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>-500</v>
-      </c>
-      <c r="C18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="10" t="n">
-        <v>-300</v>
-      </c>
-      <c r="I18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="L18" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="M18" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="N18" s="10" t="n">
-        <v>-1200</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Insurance</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="F19" s="10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="G19" s="10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="I19" s="10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="J19" s="10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="K19" s="10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="L19" s="10" t="n">
-        <v>-40</v>
-      </c>
-      <c r="M19" s="10" t="n">
-        <v>-120</v>
-      </c>
-      <c r="N19" s="10" t="n">
-        <v>-480</v>
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>Closing cash balance</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n">
+        <v>4965</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <v>4830</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <v>4587</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>4304</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <v>4011</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>3708</v>
+      </c>
+      <c r="H18" s="12" t="n">
+        <v>3435</v>
+      </c>
+      <c r="I18" s="12" t="n">
+        <v>3172</v>
+      </c>
+      <c r="J18" s="12" t="n">
+        <v>2919</v>
+      </c>
+      <c r="K18" s="12" t="n">
+        <v>2676</v>
+      </c>
+      <c r="L18" s="12" t="n">
+        <v>2443</v>
+      </c>
+      <c r="M18" s="12" t="n">
+        <v>1920</v>
+      </c>
+      <c r="N18" s="12" t="n">
+        <v>42970</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Business support / misc</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>-80</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>-80</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="G20" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="H20" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I20" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J20" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="K20" s="10" t="n">
-        <v>-110</v>
-      </c>
-      <c r="L20" s="10" t="n">
-        <v>-110</v>
-      </c>
-      <c r="M20" s="10" t="n">
-        <v>-120</v>
-      </c>
-      <c r="N20" s="10" t="n">
-        <v>-1200</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Fixed assets &amp; R&amp;D capex</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n">
-        <v>-150</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>-50</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>-50</v>
-      </c>
-      <c r="F21" s="10" t="n">
-        <v>-50</v>
-      </c>
-      <c r="G21" s="10" t="n">
-        <v>-50</v>
-      </c>
-      <c r="H21" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="I21" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="J21" s="10" t="n">
-        <v>-50</v>
-      </c>
-      <c r="K21" s="10" t="n">
-        <v>-50</v>
-      </c>
-      <c r="L21" s="10" t="n">
-        <v>-50</v>
-      </c>
-      <c r="M21" s="10" t="n">
-        <v>-100</v>
-      </c>
-      <c r="N21" s="10" t="n">
-        <v>-900</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
-        <is>
-          <t>Total Expenditure</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>-1460</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>-330</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>-460</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>-630</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>-600</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>-720</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>-4670</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>-4430</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>-4390</v>
-      </c>
-      <c r="K22" s="12" t="n">
-        <v>-4420</v>
-      </c>
-      <c r="L22" s="12" t="n">
-        <v>-4390</v>
-      </c>
-      <c r="M22" s="12" t="n">
-        <v>-4460</v>
-      </c>
-      <c r="N22" s="12" t="n">
-        <v>-30960</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Closing cash balance</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>4540</v>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>4210</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>3950</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>3670</v>
-      </c>
-      <c r="F23" s="12" t="n">
-        <v>3570</v>
-      </c>
-      <c r="G23" s="12" t="n">
-        <v>3550</v>
-      </c>
-      <c r="H23" s="12" t="n">
-        <v>149680</v>
-      </c>
-      <c r="I23" s="12" t="n">
-        <v>146350</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>143310</v>
-      </c>
-      <c r="K23" s="12" t="n">
-        <v>140590</v>
-      </c>
-      <c r="L23" s="12" t="n">
-        <v>138300</v>
-      </c>
-      <c r="M23" s="12" t="n">
-        <v>137028</v>
-      </c>
-      <c r="N23" s="12" t="n">
-        <v>878748</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Cash is positive every month: the £3,000 founder equity covers operating costs until the pre-seed bridge lands in M7 (December). Q1 marketing spend is intentionally £0 — early traction is from founder-led university outreach and the existing beta cohort.</t>
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>No founder salary is drawn in Year 1, and no institutional revenue or external funding is assumed. Cash declines steadily from the £6,000 opening balance as the business absorbs incorporation and running costs, then stabilises once modest premium-subscription revenue begins in M7 — closing the year at roughly £1,920, positive throughout.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A25:N25"/>
+    <mergeCell ref="A20:N20"/>
     <mergeCell ref="A2:N2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3466,7 +3176,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -3504,13 +3214,13 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>2100</v>
+        <v>650</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>6600</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="7">
@@ -3520,13 +3230,13 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>2100</v>
+        <v>650</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>6600</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="9">
@@ -3546,13 +3256,13 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>141028</v>
+        <v>1920</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>821256</v>
+        <v>8220</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>847776</v>
+        <v>16420</v>
       </c>
     </row>
     <row r="11">
@@ -3562,13 +3272,13 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>6200</v>
+        <v>500</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>22000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="12">
@@ -3594,13 +3304,13 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>141828</v>
+        <v>1920</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>827456</v>
+        <v>8720</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>869776</v>
+        <v>17920</v>
       </c>
     </row>
     <row r="15">
@@ -3610,13 +3320,13 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>142428</v>
+        <v>2370</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>829556</v>
+        <v>9370</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>876376</v>
+        <v>19070</v>
       </c>
     </row>
     <row r="17">
@@ -3632,17 +3342,17 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Trade payables / accrued payroll</t>
+          <t>Trade payables / accrued costs</t>
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>4200</v>
+        <v>1000</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>9800</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="19">
@@ -3668,13 +3378,13 @@
         </is>
       </c>
       <c r="B20" s="12" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>4200</v>
+        <v>1000</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>9800</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="22">
@@ -3684,13 +3394,13 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>141028</v>
+        <v>2370</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>825356</v>
+        <v>8370</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>866576</v>
+        <v>16370</v>
       </c>
     </row>
     <row r="24">
@@ -3710,29 +3420,29 @@
         </is>
       </c>
       <c r="B25" s="10" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="C25" s="10" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="D25" s="10" t="n">
-        <v>3000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Share premium (pre-seed + seed)</t>
+          <t>Share premium (none — no external investment round)</t>
         </is>
       </c>
       <c r="B26" s="10" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="C26" s="10" t="n">
-        <v>900000</v>
+        <v>0</v>
       </c>
       <c r="D26" s="10" t="n">
-        <v>900000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -3742,13 +3452,13 @@
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>-14372</v>
+        <v>-3630</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>-87144</v>
+        <v>2370</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>-65624</v>
+        <v>10370</v>
       </c>
     </row>
     <row r="28">
@@ -3758,29 +3468,29 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>138628</v>
+        <v>2370</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>815856</v>
+        <v>8370</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>837376</v>
+        <v>16370</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Balance check</t>
+          <t>Balance check (should be £0)</t>
         </is>
       </c>
       <c r="B30" s="10" t="n">
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="C30" s="10" t="n">
-        <v>9500</v>
+        <v>0</v>
       </c>
       <c r="D30" s="10" t="n">
-        <v>29200</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3797,10 +3507,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -3817,7 +3527,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -3850,16 +3560,16 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>15988</v>
+        <v>600</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>175808</v>
+        <v>16000</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>659280</v>
+        <v>48000</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>851076</v>
+        <v>64600</v>
       </c>
     </row>
     <row r="7">
@@ -3876,251 +3586,213 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Paying institutions (avg active during year)</t>
+          <t>Paying institutions (avg during year) — contingent, not signed</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="10" t="n">
         <v>0.5</v>
       </c>
-      <c r="C8" s="10" t="n">
-        <v>4</v>
-      </c>
       <c r="D8" s="10" t="n">
-        <v>14</v>
+        <v>1.5</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>18.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Paying institutions (end of year)</t>
+          <t>Price per enrolled student (£/yr)</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" s="10" t="n">
         <v>6</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>20</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>27</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Price per enrolled student (£/yr)</t>
+          <t>Average enrolled students per institution</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>2</v>
+        <v>10000</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>2</v>
+        <v>10000</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>2</v>
+        <v>10000</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>6</v>
+        <v>30000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Average enrolled students per institution</t>
+          <t>Average contract value (£/yr)</t>
         </is>
       </c>
       <c r="B11" s="10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Subtotal revenue</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="12" t="n">
         <v>10000</v>
       </c>
-      <c r="C11" s="10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E11" s="10" t="n">
+      <c r="D12" s="12" t="n">
         <v>30000</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Average contract value (£/yr)</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C12" s="10" t="n">
-        <v>20000</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
-        <is>
-          <t>Subtotal revenue</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>280000</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>370000</v>
-      </c>
+      <c r="E12" s="12" t="n">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>Service 2 — DEQUAD Premium (B2C)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n"/>
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>Service 2 — DEQUAD Premium (B2C)</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="8" t="n"/>
-      <c r="D15" s="8" t="n"/>
-      <c r="E15" s="8" t="n"/>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Paying student subs (avg, year) — independent of any pilot</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>420</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Paying student subs (avg, year)</t>
+          <t>Price per student (£/month)</t>
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>100</v>
+        <v>4.99</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1600</v>
+        <v>4.99</v>
       </c>
       <c r="D16" s="10" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>14.97</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>Subtotal revenue</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="n">
+        <v>600</v>
+      </c>
+      <c r="C17" s="12" t="n">
         <v>6000</v>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>7700</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Price per student (£/month)</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>14.97</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="D17" s="12" t="n">
+        <v>18000</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>24600</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>Service 3 — NHS ICB</t>
+        </is>
+      </c>
+      <c r="B19" s="8" t="n"/>
+      <c r="C19" s="8" t="n"/>
+      <c r="D19" s="8" t="n"/>
+      <c r="E19" s="8" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Number of contracts (not assumed in this 3-year plan)</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>Subtotal revenue</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
-        <v>5988</v>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>95808</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>359280</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <v>461076</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>Service 3 — NHS ICB pilot</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Number of contracts</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Average contract value (£/yr)</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>20000</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>Subtotal revenue</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="12" t="n">
-        <v>20000</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>20000</v>
+      <c r="B21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4157,7 +3829,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -4190,16 +3862,16 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>1440</v>
+        <v>1400</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>15600</v>
+        <v>3100</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>54000</v>
+        <v>6100</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>71040</v>
+        <v>10600</v>
       </c>
     </row>
     <row r="6">
@@ -4209,16 +3881,16 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>480</v>
+        <v>600</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>5400</v>
+        <v>1200</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>18000</v>
+        <v>2400</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>23880</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="7">
@@ -4228,35 +3900,35 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>360</v>
+        <v>400</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>4200</v>
+        <v>900</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>14400</v>
+        <v>1800</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>18960</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Stripe processing (~2.9% + 30p)</t>
+          <t>Stripe processing</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>90</v>
+      </c>
+      <c r="D8" s="10" t="n">
         <v>180</v>
       </c>
-      <c r="C8" s="10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>12000</v>
-      </c>
       <c r="E8" s="10" t="n">
-        <v>15180</v>
+        <v>320</v>
       </c>
     </row>
     <row r="9">
@@ -4266,16 +3938,16 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>1800</v>
+        <v>410</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>6000</v>
+        <v>800</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>7980</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="10">
@@ -4285,16 +3957,16 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>3600</v>
+        <v>920</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>5040</v>
+        <v>1620</v>
       </c>
     </row>
   </sheetData>
@@ -4311,14 +3983,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4331,7 +4002,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -4343,15 +4014,10 @@
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Y1 Months paid</t>
+          <t>Y2 Gross</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Y2 Gross</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>Y3 Gross</t>
         </is>
@@ -4360,308 +4026,142 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Founder A — CEO (Yusuf Quadri), £1,500/mo from M7</t>
+          <t>Founder A — CEO (Yusuf Quadri), £500/mo from Y3 only</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>9000</v>
-      </c>
-      <c r="C5" s="14" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>36000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Founder B — CTO, £1,500/mo from M7</t>
+          <t>Founder B — CTO (Yusuff Adeagbo), £500/mo from Y3 only</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>9000</v>
-      </c>
-      <c r="C6" s="14" t="n">
-        <v>6</v>
+        <v>0</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>24000</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>36000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Customer Success Manager</t>
+          <t>Safeguarding &amp; Trust Lead (part-time, ~10 hrs/wk, Y3 only — contingent on 2+ paying universities)</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>32000</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>36000</v>
+        <v>8000</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer (start Q1 Y2)</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <v>48000</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>56000</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Safeguarding &amp; Trust Lead (start Q2 Y2)</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C9" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>18000</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>42000</v>
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>Total gross salaries</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>20000</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Marketing &amp; Partnerships (start Q3 Y2)</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>38000</v>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Employer NI (13.8% above secondary threshold)</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>900</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Data / ML Engineer (start Q2 Y3)</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C11" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>40000</v>
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Employer pension (3% above £6,240)</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>350</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Mobile Engineer (start Q3 Y3)</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C12" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>25000</v>
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Other employment costs (kit, training)</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="12" t="n">
+        <v>250</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Founders' Associate (start Q3 Y3)</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Engineer #2 (start Q4 Y3)</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>12000</v>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>TOTAL EMPLOYMENT COST</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>21500</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>CSM #2 (start Q4 Y3)</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>13000</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Total gross salaries</t>
-        </is>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C16" s="15" t="inlineStr"/>
-      <c r="D16" s="12" t="n">
-        <v>156000</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>352000</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
-        <is>
-          <t>Employer NI (13.8% above secondary threshold)</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C18" s="15" t="inlineStr"/>
-      <c r="D18" s="12" t="n">
-        <v>14000</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <v>38500</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>Employer pension (3% above £6,240)</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>540</v>
-      </c>
-      <c r="C19" s="15" t="inlineStr"/>
-      <c r="D19" s="12" t="n">
-        <v>4680</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <v>11160</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t>Other employment costs (kit, training, EMI admin)</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>600</v>
-      </c>
-      <c r="C20" s="15" t="inlineStr"/>
-      <c r="D20" s="12" t="n">
-        <v>6000</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>16000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>TOTAL EMPLOYMENT COST</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>20340</v>
-      </c>
-      <c r="C21" s="15" t="inlineStr"/>
-      <c r="D21" s="12" t="n">
-        <v>180680</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <v>417660</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
-        <is>
-          <t>Founders take £0 in Q1-Q2 Y1 and £1,500/month each from M7 (Sep Y1) when the £150k pre-seed lands. Both founders accept materially below-market compensation through Y2 to preserve runway. EMI share-option scheme covers all Y2+ hires.</t>
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>No team member — founders included — draws any salary in Y1 or Y2. Both founders fund personal living costs from existing employment/freelance income throughout. Modest founder pay and the plan's only funded hire begin in Y3, funded entirely by revenue — not by any external funding round, none of which is assumed in this plan. Further hires beyond Year 3 would only be made if revenue growth or a future funding round justifies them.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4673,7 +4173,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4693,7 +4193,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. NatWest Accelerator covers office, legal and accountancy for the first 12 months.</t>
+          <t>All figures in GBP, net of VAT. Forecast — not a guarantee. No institutional revenue is assumed in Y1; no pre-seed, seed or other external funding is assumed anywhere in this model. NatWest Accelerator covers office, legal and accountancy in-kind for Year 1 only.</t>
         </is>
       </c>
     </row>
@@ -4726,16 +4226,16 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>3600</v>
+        <v>900</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>28000</v>
+        <v>2500</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>92000</v>
+        <v>5000</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>123600</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="7">
@@ -4752,39 +4252,39 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>University partnership &amp; PR (NatWest network helps)</t>
+          <t>University partnership &amp; PR (NatWest network)</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>6000</v>
+        <v>700</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>18000</v>
+        <v>1300</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>25200</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>Content / SEO / whitepaper</t>
+          <t>Content / SEO (founder-written)</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>3500</v>
+        <v>400</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>12000</v>
+        <v>700</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>16100</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="10">
@@ -4797,51 +4297,51 @@
         <v>0</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>4000</v>
+        <v>300</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>14000</v>
+        <v>700</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>18000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Instagram / TikTok (mostly organic Y1)</t>
+          <t>Instagram / TikTok (organic)</t>
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>7500</v>
+        <v>500</v>
       </c>
       <c r="D11" s="10" t="n">
-        <v>22000</v>
+        <v>1000</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>30100</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Google Search ads</t>
+          <t>Google Search ads (none in Y1)</t>
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>3000</v>
+        <v>200</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>10000</v>
+        <v>500</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>13300</v>
+        <v>700</v>
       </c>
     </row>
     <row r="13">
@@ -4851,16 +4351,16 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>900</v>
+        <v>300</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>16000</v>
+        <v>800</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>20900</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="15">
@@ -4882,17 +4382,17 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>13%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr"/>
@@ -4900,59 +4400,25 @@
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Number of campaigns / year</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="D17" s="10" t="n">
-        <v>32</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Average CAC — institutional buyer (£)</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C18" s="10" t="n">
-        <v>1800</v>
-      </c>
-      <c r="D18" s="10" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>6600</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Average CAC — premium student (£)</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D19" s="10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>9.800000000000001</v>
-      </c>
+          <t>Avg CAC per university (founder-led, low-cost)</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>~£2,500</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>~£3,300</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/visa_appendices/DEQUAD_Financial_Model.xlsx
+++ b/visa_appendices/DEQUAD_Financial_Model.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L 3yr" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cash Flow 3yr" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flow Y1 (mo)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Balance Sheet 3yr" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Revenue W1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Cost of Sales W2" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Payroll W3" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Marketing W4" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="R&amp;D W5" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Fixed Assets" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Accelerator Value" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="Startup Loan" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L 3yr" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow 3yr" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Y1 (mo)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet 3yr" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revenue W1" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cost of Sales W2" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Payroll W3" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Marketing W4" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="R&amp;D W5" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Assets" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accelerator Value" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Startup Loan" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upside Case (Y3)" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,10 +29,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="£#,##0;[Red](£#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,6 +76,26 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F2942"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="004F6076"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="000F2942"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -125,7 +148,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,6 +194,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -717,146 +754,167 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  - Office, legal and accountancy carry a nominal £0 cash cost in Y1 because</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - See the "Upside Case (Y3)" sheet for the job-creation-target scenario (5 full-time</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    those services are provided FREE by the NatWest Accelerator (Y1 only).</t>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    hires, avg £25,000/yr, meeting the Innovator Founder settlement job-creation criterion).</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Marketing is founder-led and low-cost throughout — no paid-acquisition</t>
+          <t xml:space="preserve">  - Office, legal and accountancy carry a nominal £0 cash cost in Y1 because</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    budget in Y1; spend grows only in line with actual revenue in Y2-Y3.</t>
+          <t xml:space="preserve">    those services are provided FREE by the NatWest Accelerator (Y1 only).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">  - Marketing is founder-led and low-cost throughout — no paid-acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    budget in Y1; spend grows only in line with actual revenue in Y2-Y3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">  - Y1 starts with the existing MVP, so no upfront engineering capex.</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>WORKBOOK STRUCTURE</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. P&amp;L 3yr            — Annual Profit &amp; Loss</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2. Cash Flow 3yr      — Annual cash flow forecast</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3. Cash Flow Y1 (mo)  — Monthly cash flow for Year 1</t>
+          <t xml:space="preserve">  1. P&amp;L 3yr            — Annual Profit &amp; Loss</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4. Balance Sheet 3yr  — Year-end balance sheets</t>
+          <t xml:space="preserve">  2. Cash Flow 3yr      — Annual cash flow forecast</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5. Revenue W1         — Revenue detail by service</t>
+          <t xml:space="preserve">  3. Cash Flow Y1 (mo)  — Monthly cash flow for Year 1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  6. Cost of Sales W2   — Direct cost detail</t>
+          <t xml:space="preserve">  4. Balance Sheet 3yr  — Year-end balance sheets</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  7. Payroll W3         — Salaries, NI and pension</t>
+          <t xml:space="preserve">  5. Revenue W1         — Revenue detail by service</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  8. Marketing W4       — Marketing spend by channel</t>
+          <t xml:space="preserve">  6. Cost of Sales W2   — Direct cost detail</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  9. R&amp;D W5             — R&amp;D activity (unpaid founder time; no tax credit assumed)</t>
+          <t xml:space="preserve">  7. Payroll W3         — Salaries, NI and pension</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 10. Fixed Assets       — CAPEX schedule</t>
+          <t xml:space="preserve">  8. Marketing W4       — Marketing spend by channel</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 11. Accelerator Value  — Quantified in-kind value of NatWest support (Y1 only)</t>
+          <t xml:space="preserve">  9. R&amp;D W5             — R&amp;D activity (unpaid founder time; no tax credit assumed)</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 12. Startup Loan       — Empty (no debt taken; no external funding assumed at all)</t>
+          <t xml:space="preserve"> 10. Fixed Assets       — CAPEX schedule</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr"/>
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 11. Accelerator Value  — Quantified in-kind value of NatWest support (Y1 only)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve"> 12. Startup Loan       — Empty (no debt taken; no external funding assumed at all)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 13. Upside Case (Y3)  — Illustrative Y3 P&amp;L for the 5-hire job-creation target</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>All assumptions map to DEQUAD_UKES_Business_Plan.md (v5.0, self-funded revision).</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Yellow cells indicate user-editable inputs.</t>
         </is>
@@ -1420,6 +1478,629 @@
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A6:E6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="19" t="inlineStr">
+        <is>
+          <t>Upside Case — Job-Creation Target (Year 3 only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="60" customHeight="1">
+      <c r="A2" s="20" t="inlineStr">
+        <is>
+          <t>ILLUSTRATIVE — not part of the core 3-year self-funded forecast (see P&amp;L 3yr / Payroll W3). This scenario shows what Year 3 would look like if institutional revenue scales beyond the conservative base case via pilot conversion (5+ paying universities), funding the plan's job-creation target of 5 full-time UK hires (Student Ambassador, Social Media Manager, Marketing Intern, Sales Lead, Support Agent — Appendix G), each sustained 12+ months at an average salary of £25,000/year, meeting the Innovator Founder settlement job-creation criterion. Years 1-2 are identical to the base case (no institutional revenue is assumed until pilot conversion). Figures are a founder-prepared illustrative projection, not a commitment.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="21" t="n"/>
+      <c r="B4" s="22" t="inlineStr">
+        <is>
+          <t>Y3 Base Case</t>
+        </is>
+      </c>
+      <c r="C4" s="22" t="inlineStr">
+        <is>
+          <t>Y3 Upside Case</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="n"/>
+      <c r="C5" s="24" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Institutional (universities, £20,000/yr each)</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Institutional — university count (avg in year)</t>
+        </is>
+      </c>
+      <c r="B7" s="26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Premium (DEQUAD Premium, £59.88/yr avg)</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>90000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Premium — avg subscribers</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n">
+        <v>300</v>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="28" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Cost of Sales</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Cloud hosting (Render, Cloudflare)</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C13" s="25" t="n">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>LLM / safeguarding inference</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>7200</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stripe processing</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="n">
+        <v>180</v>
+      </c>
+      <c r="C15" s="25" t="n">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SMS &amp; email (Twilio, SendGrid)</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="n">
+        <v>800</v>
+      </c>
+      <c r="C16" s="25" t="n">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Customer-success tooling</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="n">
+        <v>920</v>
+      </c>
+      <c r="C17" s="25" t="n">
+        <v>3700</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="28" t="inlineStr">
+        <is>
+          <t>Total Cost of Sales</t>
+        </is>
+      </c>
+      <c r="B18" s="29" t="n">
+        <v>6100</v>
+      </c>
+      <c r="C18" s="29" t="n">
+        <v>24600</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="28" t="inlineStr">
+        <is>
+          <t>Gross Profit / (Loss)</t>
+        </is>
+      </c>
+      <c r="B20" s="29" t="n">
+        <v>41900</v>
+      </c>
+      <c r="C20" s="29" t="n">
+        <v>185400</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B21" s="30" t="n">
+        <v>0.873</v>
+      </c>
+      <c r="C21" s="30" t="n">
+        <v>0.883</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Payroll (Year 3)</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="24" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Founder A — CEO, £500/mo</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Founder B — CTO, £500/mo</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Safeguarding &amp; Trust Lead (part-time) — base case only</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C26" s="25" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Student Ambassador — full-time, £25,000/yr</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Social Media Manager — full-time, £25,000/yr</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="25" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Marketing Intern — full-time, £25,000/yr</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="n"/>
+      <c r="C29" s="25" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sales Lead — full-time, £25,000/yr</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="n"/>
+      <c r="C30" s="25" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Support Agent — full-time, £25,000/yr</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="n"/>
+      <c r="C31" s="25" t="n">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Total gross salaries</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>137000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Employer NI (13.8% above secondary threshold)</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="n">
+        <v>900</v>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>11000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Employer pension (3% above £6,240)</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="n">
+        <v>350</v>
+      </c>
+      <c r="C34" s="25" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Other employment costs (kit, onboarding, training)</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="n">
+        <v>250</v>
+      </c>
+      <c r="C35" s="25" t="n">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>Total Employment Cost</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="n">
+        <v>21500</v>
+      </c>
+      <c r="C36" s="29" t="n">
+        <v>152050</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>Other Operating Expenses</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="n"/>
+      <c r="C38" s="24" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Marketing (paid channels, campaigns)</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C39" s="25" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Software subscriptions (incl. CRM, helpdesk)</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C40" s="25" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Office / co-working (7 people vs 3)</t>
+        </is>
+      </c>
+      <c r="B41" s="25" t="n">
+        <v>600</v>
+      </c>
+      <c r="C41" s="25" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Legal &amp; accountancy</t>
+        </is>
+      </c>
+      <c r="B42" s="25" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C42" s="25" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Insurance (D&amp;O, PI, Cyber, EL)</t>
+        </is>
+      </c>
+      <c r="B43" s="25" t="n">
+        <v>900</v>
+      </c>
+      <c r="C43" s="25" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Business support / misc</t>
+        </is>
+      </c>
+      <c r="B44" s="25" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C44" s="25" t="n">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Fixed assets capex (kit for new hires)</t>
+        </is>
+      </c>
+      <c r="B45" s="25" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C45" s="25" t="n">
+        <v>2800</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="28" t="inlineStr">
+        <is>
+          <t>Total Other OPEX</t>
+        </is>
+      </c>
+      <c r="B46" s="29" t="n">
+        <v>11700</v>
+      </c>
+      <c r="C46" s="29" t="n">
+        <v>34300</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="28" t="inlineStr">
+        <is>
+          <t>TOTAL OPEX (incl. payroll)</t>
+        </is>
+      </c>
+      <c r="B48" s="29" t="n">
+        <v>33200</v>
+      </c>
+      <c r="C48" s="29" t="n">
+        <v>186350</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="28" t="inlineStr">
+        <is>
+          <t>Operating Result</t>
+        </is>
+      </c>
+      <c r="B50" s="29" t="n">
+        <v>9200</v>
+      </c>
+      <c r="C50" s="29" t="n">
+        <v>-950</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="23" t="inlineStr">
+        <is>
+          <t>Cash Flow Impact (Year 3)</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="n"/>
+      <c r="C53" s="24" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Opening cash (Y3, identical in both cases — from shared Y1-Y2)</t>
+        </is>
+      </c>
+      <c r="B54" s="25" t="n">
+        <v>8220</v>
+      </c>
+      <c r="C54" s="25" t="n">
+        <v>8220</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Total receipts (= Total Revenue above)</t>
+        </is>
+      </c>
+      <c r="B55" s="25" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C55" s="25" t="n">
+        <v>210000</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="28" t="inlineStr">
+        <is>
+          <t>Total expenditure (COGS + Total Employment Cost + Other OPEX + Corp tax)</t>
+        </is>
+      </c>
+      <c r="B56" s="29" t="n">
+        <v>-39800</v>
+      </c>
+      <c r="C56" s="29" t="n">
+        <v>-211450</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="28" t="inlineStr">
+        <is>
+          <t>Net cash movement in year</t>
+        </is>
+      </c>
+      <c r="B57" s="29" t="n">
+        <v>8200</v>
+      </c>
+      <c r="C57" s="29" t="n">
+        <v>-1450</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="28" t="inlineStr">
+        <is>
+          <t>Closing cash</t>
+        </is>
+      </c>
+      <c r="B58" s="29" t="n">
+        <v>16420</v>
+      </c>
+      <c r="C58" s="29" t="n">
+        <v>6770</v>
+      </c>
+    </row>
+    <row r="59" ht="60" customHeight="1">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>Reconciliation note: this upside case ends Year 3 with £6,770 of cash on the books (down from the base case's £16,420, since the extra wage bill outpaces the extra revenue slightly) but does not require any external funding — it is funded entirely by the additional institutional and premium revenue generated once 5+ universities convert post-pilot. This is an annual figure only; no month-by-month cash flow has been modelled for this scenario, so intra-year dips (e.g. before new hires' revenue impact ramps up) are not ruled out. Presented as an illustrative target, not a committed forecast — the core 3-year model (P&amp;L 3yr, Payroll W3) remains the conservative base case this business plan is built on.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/visa_appendices/DEQUAD_Financial_Model.xlsx
+++ b/visa_appendices/DEQUAD_Financial_Model.xlsx
@@ -1507,7 +1507,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="20" t="inlineStr">
         <is>
-          <t>ILLUSTRATIVE — not part of the core 3-year self-funded forecast (see P&amp;L 3yr / Payroll W3). This scenario shows what Year 3 would look like if institutional revenue scales beyond the conservative base case via pilot conversion (5+ paying universities), funding the plan's job-creation target of 5 full-time UK hires (Student Ambassador, Social Media Manager, Marketing Intern, Sales Lead, Support Agent — Appendix G), each sustained 12+ months at an average salary of £25,000/year, meeting the Innovator Founder settlement job-creation criterion. Years 1-2 are identical to the base case (no institutional revenue is assumed until pilot conversion). Figures are a founder-prepared illustrative projection, not a commitment.</t>
+          <t>ILLUSTRATIVE — not part of the core 3-year self-funded forecast (see P&amp;L 3yr / Payroll W3). This scenario shows what Year 3 would look like if institutional revenue scales beyond the conservative base case via pilot conversion (6+ paying universities), funding the plan's job-creation target of 3 full-time UK hires (Sales Lead, Support Agent, Student Ambassador — Appendix G), each sustained 12+ months at an average salary of £25,000/year, meeting the Innovator Founder settlement job-creation criterion. Years 1-2 are identical to the base case (no institutional revenue is assumed until pilot conversion). Figures are a founder-prepared illustrative projection, not a commitment.</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Student Ambassador — full-time, £25,000/yr</t>
+          <t>Sales Lead — full-time, £25,000/yr</t>
         </is>
       </c>
       <c r="B27" s="25" t="n"/>
@@ -1771,7 +1771,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Social Media Manager — full-time, £25,000/yr</t>
+          <t>Support Agent — full-time, £25,000/yr</t>
         </is>
       </c>
       <c r="B28" s="25" t="n"/>
@@ -1782,7 +1782,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Marketing Intern — full-time, £25,000/yr</t>
+          <t>Student Ambassador — full-time, £25,000/yr</t>
         </is>
       </c>
       <c r="B29" s="25" t="n"/>
@@ -1791,26 +1791,12 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Sales Lead — full-time, £25,000/yr</t>
-        </is>
-      </c>
       <c r="B30" s="25" t="n"/>
-      <c r="C30" s="25" t="n">
-        <v>25000</v>
-      </c>
+      <c r="C30" s="25" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Support Agent — full-time, £25,000/yr</t>
-        </is>
-      </c>
       <c r="B31" s="25" t="n"/>
-      <c r="C31" s="25" t="n">
-        <v>25000</v>
-      </c>
+      <c r="C31" s="25" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1822,7 +1808,7 @@
         <v>20000</v>
       </c>
       <c r="C32" s="25" t="n">
-        <v>137000</v>
+        <v>87000</v>
       </c>
     </row>
     <row r="33">
@@ -1835,7 +1821,7 @@
         <v>900</v>
       </c>
       <c r="C33" s="25" t="n">
-        <v>11000</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="34">
@@ -1848,7 +1834,7 @@
         <v>350</v>
       </c>
       <c r="C34" s="25" t="n">
-        <v>2800</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="35">
@@ -1861,7 +1847,7 @@
         <v>250</v>
       </c>
       <c r="C35" s="25" t="n">
-        <v>1250</v>
+        <v>750</v>
       </c>
     </row>
     <row r="36">
@@ -1874,7 +1860,7 @@
         <v>21500</v>
       </c>
       <c r="C36" s="29" t="n">
-        <v>152050</v>
+        <v>96050</v>
       </c>
     </row>
     <row r="38">
@@ -1915,14 +1901,14 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Office / co-working (7 people vs 3)</t>
+          <t>Office / co-working (5 people vs 3)</t>
         </is>
       </c>
       <c r="B41" s="25" t="n">
         <v>600</v>
       </c>
       <c r="C41" s="25" t="n">
-        <v>3000</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="42">
@@ -1974,7 +1960,7 @@
         <v>1200</v>
       </c>
       <c r="C45" s="25" t="n">
-        <v>2800</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="46">
@@ -1987,7 +1973,7 @@
         <v>11700</v>
       </c>
       <c r="C46" s="29" t="n">
-        <v>34300</v>
+        <v>32650</v>
       </c>
     </row>
     <row r="48">
@@ -2000,7 +1986,7 @@
         <v>33200</v>
       </c>
       <c r="C48" s="29" t="n">
-        <v>186350</v>
+        <v>128700</v>
       </c>
     </row>
     <row r="50">
@@ -2013,7 +1999,7 @@
         <v>9200</v>
       </c>
       <c r="C50" s="29" t="n">
-        <v>-950</v>
+        <v>56700</v>
       </c>
     </row>
     <row r="53">
@@ -2061,7 +2047,7 @@
         <v>-39800</v>
       </c>
       <c r="C56" s="29" t="n">
-        <v>-211450</v>
+        <v>-153800</v>
       </c>
     </row>
     <row r="57">
@@ -2074,7 +2060,7 @@
         <v>8200</v>
       </c>
       <c r="C57" s="29" t="n">
-        <v>-1450</v>
+        <v>56200</v>
       </c>
     </row>
     <row r="58">
@@ -2087,13 +2073,13 @@
         <v>16420</v>
       </c>
       <c r="C58" s="29" t="n">
-        <v>6770</v>
+        <v>64420</v>
       </c>
     </row>
     <row r="59" ht="60" customHeight="1">
       <c r="A59" s="20" t="inlineStr">
         <is>
-          <t>Reconciliation note: this upside case ends Year 3 with £6,770 of cash on the books (down from the base case's £16,420, since the extra wage bill outpaces the extra revenue slightly) but does not require any external funding — it is funded entirely by the additional institutional and premium revenue generated once 5+ universities convert post-pilot. This is an annual figure only; no month-by-month cash flow has been modelled for this scenario, so intra-year dips (e.g. before new hires' revenue impact ramps up) are not ruled out. Presented as an illustrative target, not a committed forecast — the core 3-year model (P&amp;L 3yr, Payroll W3) remains the conservative base case this business plan is built on.</t>
+          <t>Reconciliation note: this upside case ends Year 3 with £64,420 of cash on the books (up from the base case's £16,420, since the leaner 3-hire cost base is more than covered by the additional institutional and premium revenue once 6+ universities and 1,500 premium subscribers are reached) — funded entirely by that additional revenue, not any external funding. This is an annual figure only; no month-by-month cash flow has been modelled for this scenario, so intra-year timing dips (e.g. before new hires' revenue impact ramps up, or before institutional invoices are collected) are not ruled out. Presented as an illustrative target, not a committed forecast — the core 3-year model (P&amp;L 3yr, Payroll W3) remains the conservative base case this business plan is built on.</t>
         </is>
       </c>
     </row>

--- a/visa_appendices/DEQUAD_Financial_Model.xlsx
+++ b/visa_appendices/DEQUAD_Financial_Model.xlsx
@@ -599,7 +599,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Entity:       DEQUAD Ltd (company in formation, England &amp; Wales)</t>
+          <t>Entity:       DEQUAD Ltd (Company No. 17405964, incorporated in England &amp; Wales)</t>
         </is>
       </c>
     </row>

--- a/visa_appendices/DEQUAD_Financial_Model.xlsx
+++ b/visa_appendices/DEQUAD_Financial_Model.xlsx
@@ -2181,7 +2181,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>6000</v>
@@ -2190,7 +2190,7 @@
         <v>18000</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>24600</v>
+        <v>24150</v>
       </c>
     </row>
     <row r="8">
@@ -2219,7 +2219,7 @@
         </is>
       </c>
       <c r="B9" s="12" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="C9" s="12" t="n">
         <v>16000</v>
@@ -2228,7 +2228,7 @@
         <v>48000</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>64600</v>
+        <v>64150</v>
       </c>
     </row>
     <row r="11">
@@ -2363,7 +2363,7 @@
         </is>
       </c>
       <c r="B19" s="12" t="n">
-        <v>-800</v>
+        <v>-1250</v>
       </c>
       <c r="C19" s="12" t="n">
         <v>12900</v>
@@ -2372,7 +2372,7 @@
         <v>41900</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>54000</v>
+        <v>53550</v>
       </c>
     </row>
     <row r="20">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>-133.3%</t>
+          <t>-833.3%</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="B35" s="12" t="n">
-        <v>-3480</v>
+        <v>-3930</v>
       </c>
       <c r="C35" s="12" t="n">
         <v>6900</v>
@@ -2634,7 +2634,7 @@
         <v>9900</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>13320</v>
+        <v>12870</v>
       </c>
     </row>
     <row r="36">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="B36" s="13" t="inlineStr">
         <is>
-          <t>-580.0%</t>
+          <t>-2620.0%</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -2686,7 +2686,7 @@
         </is>
       </c>
       <c r="B38" s="12" t="n">
-        <v>-3630</v>
+        <v>-4080</v>
       </c>
       <c r="C38" s="12" t="n">
         <v>6500</v>
@@ -2695,7 +2695,7 @@
         <v>9200</v>
       </c>
       <c r="E38" s="12" t="n">
-        <v>12070</v>
+        <v>11620</v>
       </c>
     </row>
     <row r="39">
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>-3630</v>
+        <v>-4080</v>
       </c>
       <c r="C40" s="12" t="n">
         <v>6000</v>
@@ -2733,7 +2733,7 @@
         <v>8000</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>10370</v>
+        <v>9920</v>
       </c>
     </row>
   </sheetData>
@@ -2800,10 +2800,10 @@
         <v>6000</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>1920</v>
+        <v>1470</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>8220</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="6">
@@ -2833,7 +2833,7 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>16000</v>
@@ -2849,7 +2849,7 @@
         </is>
       </c>
       <c r="B10" s="12" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="C10" s="12" t="n">
         <v>16000</v>
@@ -3051,7 +3051,7 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>-4080</v>
+        <v>-4530</v>
       </c>
       <c r="C25" s="12" t="n">
         <v>6300</v>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>1920</v>
+        <v>1470</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>8220</v>
+        <v>7770</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>16420</v>
+        <v>15970</v>
       </c>
     </row>
     <row r="28">
@@ -3238,22 +3238,22 @@
         <v>3708</v>
       </c>
       <c r="I5" s="10" t="n">
-        <v>3435</v>
+        <v>3395</v>
       </c>
       <c r="J5" s="10" t="n">
-        <v>3172</v>
+        <v>3077</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>2919</v>
+        <v>2754</v>
       </c>
       <c r="L5" s="10" t="n">
-        <v>2676</v>
+        <v>2426</v>
       </c>
       <c r="M5" s="10" t="n">
-        <v>2443</v>
+        <v>2098</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>47050</v>
+        <v>46155</v>
       </c>
     </row>
     <row r="6">
@@ -3301,25 +3301,25 @@
         <v>0</v>
       </c>
       <c r="H7" s="10" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I7" s="10" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="J7" s="10" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K7" s="10" t="n">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="L7" s="10" t="n">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="M7" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="N7" s="10" t="n">
         <v>150</v>
-      </c>
-      <c r="N7" s="10" t="n">
-        <v>600</v>
       </c>
     </row>
     <row r="8">
@@ -3347,25 +3347,25 @@
         <v>0</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>70</v>
+        <v>15</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K8" s="12" t="n">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>130</v>
+        <v>35</v>
       </c>
       <c r="M8" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="N8" s="12" t="n">
         <v>150</v>
-      </c>
-      <c r="N8" s="12" t="n">
-        <v>600</v>
       </c>
     </row>
     <row r="9">
@@ -3781,31 +3781,31 @@
         <v>3708</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>3435</v>
+        <v>3395</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>3172</v>
+        <v>3077</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>2919</v>
+        <v>2754</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>2676</v>
+        <v>2426</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>2443</v>
+        <v>2098</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>1920</v>
+        <v>1470</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>42970</v>
+        <v>41625</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>No founder salary is drawn in Year 1, and no institutional revenue or external funding is assumed. Cash declines steadily from the £6,000 opening balance as the business absorbs incorporation and running costs, then stabilises once modest premium-subscription revenue begins in M7 — closing the year at roughly £1,920, positive throughout.</t>
+          <t>No founder salary is drawn in Year 1, and no institutional revenue or external funding is assumed. Cash declines steadily from the £6,000 opening balance as the business absorbs incorporation and running costs, then stabilises once modest premium-subscription revenue begins in M7 — closing the year at roughly £1,470, positive throughout.</t>
         </is>
       </c>
     </row>
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>1920</v>
+        <v>1470</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>8220</v>
+        <v>7770</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>16420</v>
+        <v>15970</v>
       </c>
     </row>
     <row r="11">
@@ -3971,13 +3971,13 @@
         </is>
       </c>
       <c r="B13" s="12" t="n">
-        <v>1920</v>
+        <v>1470</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>8720</v>
+        <v>8270</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>17920</v>
+        <v>17470</v>
       </c>
     </row>
     <row r="15">
@@ -3987,13 +3987,13 @@
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>2370</v>
+        <v>1920</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>9370</v>
+        <v>8920</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>19070</v>
+        <v>18620</v>
       </c>
     </row>
     <row r="17">
@@ -4061,13 +4061,13 @@
         </is>
       </c>
       <c r="B22" s="12" t="n">
-        <v>2370</v>
+        <v>1920</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>8370</v>
+        <v>7920</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>16370</v>
+        <v>15920</v>
       </c>
     </row>
     <row r="24">
@@ -4119,13 +4119,13 @@
         </is>
       </c>
       <c r="B27" s="10" t="n">
-        <v>-3630</v>
+        <v>-4080</v>
       </c>
       <c r="C27" s="10" t="n">
-        <v>2370</v>
+        <v>1920</v>
       </c>
       <c r="D27" s="10" t="n">
-        <v>10370</v>
+        <v>9920</v>
       </c>
     </row>
     <row r="28">
@@ -4135,13 +4135,13 @@
         </is>
       </c>
       <c r="B28" s="12" t="n">
-        <v>2370</v>
+        <v>1920</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>8370</v>
+        <v>7920</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>16370</v>
+        <v>15920</v>
       </c>
     </row>
     <row r="30">
@@ -4227,7 +4227,7 @@
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="C5" s="12" t="n">
         <v>16000</v>
@@ -4236,7 +4236,7 @@
         <v>48000</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>64600</v>
+        <v>64150</v>
       </c>
     </row>
     <row r="7">
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C15" s="10" t="n">
         <v>100</v>
@@ -4372,7 +4372,7 @@
         <v>300</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>420</v>
+        <v>405</v>
       </c>
     </row>
     <row r="16">
@@ -4401,7 +4401,7 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="C17" s="12" t="n">
         <v>6000</v>
@@ -4410,7 +4410,7 @@
         <v>18000</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>24600</v>
+        <v>24150</v>
       </c>
     </row>
     <row r="19">
